--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2021_o_higgins.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_s_2021_o_higgins.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:44</t>
+    <t xml:space="preserve">2026-10-05 02:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>277138.94</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>325846.62</v>
+        <v>325846.63</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>287190.62</v>
+        <v>287190.63</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>339790.09</v>
